--- a/local_agent/assets/tmall_path_import/TmallImageTemplate.xlsx
+++ b/local_agent/assets/tmall_path_import/TmallImageTemplate.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:K201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -434,11 +434,12 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -469,25 +470,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>品牌标签</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>商品ID</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>活动话题</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>音乐名称</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>定时发布</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>创作者声明</t>
         </is>
@@ -519,834 +525,839 @@
           <t>女鞋,夏季穿搭</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>耐克</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>夏日上新</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>默契</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2030年12月31日 14点30分</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>内容含营销信息</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="F3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="F4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="F5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="F6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="F7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="F8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="F9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="F10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="F11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="F12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="F13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="F14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="F15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="F16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="F17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="F18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="F19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="F20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="F21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="F22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="F23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="F24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="F25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="F26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="F27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="F28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="F29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="F30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
     </row>
     <row r="31">
-      <c r="F31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="F32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="F33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="F34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="F35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="F36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="F37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="F38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="F39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
     </row>
     <row r="40">
-      <c r="F40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="F41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="F42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="F43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="F44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="F45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
     </row>
     <row r="46">
-      <c r="F46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="F47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="F48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="F49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="F50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="F51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="F52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="F53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="F54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
     </row>
     <row r="55">
-      <c r="F55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="F56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
     </row>
     <row r="57">
-      <c r="F57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="F58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="F59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
     </row>
     <row r="60">
-      <c r="F60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
     </row>
     <row r="61">
-      <c r="F61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
     </row>
     <row r="62">
-      <c r="F62" s="4" t="n"/>
-      <c r="I62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
     </row>
     <row r="63">
-      <c r="F63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="F64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
     </row>
     <row r="65">
-      <c r="F65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
     </row>
     <row r="66">
-      <c r="F66" s="4" t="n"/>
-      <c r="I66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
     </row>
     <row r="67">
-      <c r="F67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
     </row>
     <row r="68">
-      <c r="F68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
     </row>
     <row r="69">
-      <c r="F69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
     </row>
     <row r="70">
-      <c r="F70" s="4" t="n"/>
-      <c r="I70" s="4" t="n"/>
+      <c r="G70" s="4" t="n"/>
+      <c r="J70" s="4" t="n"/>
     </row>
     <row r="71">
-      <c r="F71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
+      <c r="G71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="F72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
     </row>
     <row r="73">
-      <c r="F73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="J73" s="4" t="n"/>
     </row>
     <row r="74">
-      <c r="F74" s="4" t="n"/>
-      <c r="I74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+      <c r="J74" s="4" t="n"/>
     </row>
     <row r="75">
-      <c r="F75" s="4" t="n"/>
-      <c r="I75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
     </row>
     <row r="76">
-      <c r="F76" s="4" t="n"/>
-      <c r="I76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
     </row>
     <row r="77">
-      <c r="F77" s="4" t="n"/>
-      <c r="I77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="J77" s="4" t="n"/>
     </row>
     <row r="78">
-      <c r="F78" s="4" t="n"/>
-      <c r="I78" s="4" t="n"/>
+      <c r="G78" s="4" t="n"/>
+      <c r="J78" s="4" t="n"/>
     </row>
     <row r="79">
-      <c r="F79" s="4" t="n"/>
-      <c r="I79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="J79" s="4" t="n"/>
     </row>
     <row r="80">
-      <c r="F80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
+      <c r="J80" s="4" t="n"/>
     </row>
     <row r="81">
-      <c r="F81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="J81" s="4" t="n"/>
     </row>
     <row r="82">
-      <c r="F82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
+      <c r="J82" s="4" t="n"/>
     </row>
     <row r="83">
-      <c r="F83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
     </row>
     <row r="84">
-      <c r="F84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
+      <c r="G84" s="4" t="n"/>
+      <c r="J84" s="4" t="n"/>
     </row>
     <row r="85">
-      <c r="F85" s="4" t="n"/>
-      <c r="I85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
     </row>
     <row r="86">
-      <c r="F86" s="4" t="n"/>
-      <c r="I86" s="4" t="n"/>
+      <c r="G86" s="4" t="n"/>
+      <c r="J86" s="4" t="n"/>
     </row>
     <row r="87">
-      <c r="F87" s="4" t="n"/>
-      <c r="I87" s="4" t="n"/>
+      <c r="G87" s="4" t="n"/>
+      <c r="J87" s="4" t="n"/>
     </row>
     <row r="88">
-      <c r="F88" s="4" t="n"/>
-      <c r="I88" s="4" t="n"/>
+      <c r="G88" s="4" t="n"/>
+      <c r="J88" s="4" t="n"/>
     </row>
     <row r="89">
-      <c r="F89" s="4" t="n"/>
-      <c r="I89" s="4" t="n"/>
+      <c r="G89" s="4" t="n"/>
+      <c r="J89" s="4" t="n"/>
     </row>
     <row r="90">
-      <c r="F90" s="4" t="n"/>
-      <c r="I90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
+      <c r="J90" s="4" t="n"/>
     </row>
     <row r="91">
-      <c r="F91" s="4" t="n"/>
-      <c r="I91" s="4" t="n"/>
+      <c r="G91" s="4" t="n"/>
+      <c r="J91" s="4" t="n"/>
     </row>
     <row r="92">
-      <c r="F92" s="4" t="n"/>
-      <c r="I92" s="4" t="n"/>
+      <c r="G92" s="4" t="n"/>
+      <c r="J92" s="4" t="n"/>
     </row>
     <row r="93">
-      <c r="F93" s="4" t="n"/>
-      <c r="I93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
     </row>
     <row r="94">
-      <c r="F94" s="4" t="n"/>
-      <c r="I94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
     </row>
     <row r="95">
-      <c r="F95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
     </row>
     <row r="96">
-      <c r="F96" s="4" t="n"/>
-      <c r="I96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="J96" s="4" t="n"/>
     </row>
     <row r="97">
-      <c r="F97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
     </row>
     <row r="98">
-      <c r="F98" s="4" t="n"/>
-      <c r="I98" s="4" t="n"/>
+      <c r="G98" s="4" t="n"/>
+      <c r="J98" s="4" t="n"/>
     </row>
     <row r="99">
-      <c r="F99" s="4" t="n"/>
-      <c r="I99" s="4" t="n"/>
+      <c r="G99" s="4" t="n"/>
+      <c r="J99" s="4" t="n"/>
     </row>
     <row r="100">
-      <c r="F100" s="4" t="n"/>
-      <c r="I100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
+      <c r="J100" s="4" t="n"/>
     </row>
     <row r="101">
-      <c r="F101" s="4" t="n"/>
-      <c r="I101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
+      <c r="J101" s="4" t="n"/>
     </row>
     <row r="102">
-      <c r="F102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
     </row>
     <row r="103">
-      <c r="F103" s="4" t="n"/>
-      <c r="I103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
     </row>
     <row r="104">
-      <c r="F104" s="4" t="n"/>
-      <c r="I104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
     </row>
     <row r="105">
-      <c r="F105" s="4" t="n"/>
-      <c r="I105" s="4" t="n"/>
+      <c r="G105" s="4" t="n"/>
+      <c r="J105" s="4" t="n"/>
     </row>
     <row r="106">
-      <c r="F106" s="4" t="n"/>
-      <c r="I106" s="4" t="n"/>
+      <c r="G106" s="4" t="n"/>
+      <c r="J106" s="4" t="n"/>
     </row>
     <row r="107">
-      <c r="F107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
+      <c r="J107" s="4" t="n"/>
     </row>
     <row r="108">
-      <c r="F108" s="4" t="n"/>
-      <c r="I108" s="4" t="n"/>
+      <c r="G108" s="4" t="n"/>
+      <c r="J108" s="4" t="n"/>
     </row>
     <row r="109">
-      <c r="F109" s="4" t="n"/>
-      <c r="I109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
+      <c r="J109" s="4" t="n"/>
     </row>
     <row r="110">
-      <c r="F110" s="4" t="n"/>
-      <c r="I110" s="4" t="n"/>
+      <c r="G110" s="4" t="n"/>
+      <c r="J110" s="4" t="n"/>
     </row>
     <row r="111">
-      <c r="F111" s="4" t="n"/>
-      <c r="I111" s="4" t="n"/>
+      <c r="G111" s="4" t="n"/>
+      <c r="J111" s="4" t="n"/>
     </row>
     <row r="112">
-      <c r="F112" s="4" t="n"/>
-      <c r="I112" s="4" t="n"/>
+      <c r="G112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
     </row>
     <row r="113">
-      <c r="F113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
+      <c r="G113" s="4" t="n"/>
+      <c r="J113" s="4" t="n"/>
     </row>
     <row r="114">
-      <c r="F114" s="4" t="n"/>
-      <c r="I114" s="4" t="n"/>
+      <c r="G114" s="4" t="n"/>
+      <c r="J114" s="4" t="n"/>
     </row>
     <row r="115">
-      <c r="F115" s="4" t="n"/>
-      <c r="I115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
     </row>
     <row r="116">
-      <c r="F116" s="4" t="n"/>
-      <c r="I116" s="4" t="n"/>
+      <c r="G116" s="4" t="n"/>
+      <c r="J116" s="4" t="n"/>
     </row>
     <row r="117">
-      <c r="F117" s="4" t="n"/>
-      <c r="I117" s="4" t="n"/>
+      <c r="G117" s="4" t="n"/>
+      <c r="J117" s="4" t="n"/>
     </row>
     <row r="118">
-      <c r="F118" s="4" t="n"/>
-      <c r="I118" s="4" t="n"/>
+      <c r="G118" s="4" t="n"/>
+      <c r="J118" s="4" t="n"/>
     </row>
     <row r="119">
-      <c r="F119" s="4" t="n"/>
-      <c r="I119" s="4" t="n"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="J119" s="4" t="n"/>
     </row>
     <row r="120">
-      <c r="F120" s="4" t="n"/>
-      <c r="I120" s="4" t="n"/>
+      <c r="G120" s="4" t="n"/>
+      <c r="J120" s="4" t="n"/>
     </row>
     <row r="121">
-      <c r="F121" s="4" t="n"/>
-      <c r="I121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
     </row>
     <row r="122">
-      <c r="F122" s="4" t="n"/>
-      <c r="I122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
+      <c r="J122" s="4" t="n"/>
     </row>
     <row r="123">
-      <c r="F123" s="4" t="n"/>
-      <c r="I123" s="4" t="n"/>
+      <c r="G123" s="4" t="n"/>
+      <c r="J123" s="4" t="n"/>
     </row>
     <row r="124">
-      <c r="F124" s="4" t="n"/>
-      <c r="I124" s="4" t="n"/>
+      <c r="G124" s="4" t="n"/>
+      <c r="J124" s="4" t="n"/>
     </row>
     <row r="125">
-      <c r="F125" s="4" t="n"/>
-      <c r="I125" s="4" t="n"/>
+      <c r="G125" s="4" t="n"/>
+      <c r="J125" s="4" t="n"/>
     </row>
     <row r="126">
-      <c r="F126" s="4" t="n"/>
-      <c r="I126" s="4" t="n"/>
+      <c r="G126" s="4" t="n"/>
+      <c r="J126" s="4" t="n"/>
     </row>
     <row r="127">
-      <c r="F127" s="4" t="n"/>
-      <c r="I127" s="4" t="n"/>
+      <c r="G127" s="4" t="n"/>
+      <c r="J127" s="4" t="n"/>
     </row>
     <row r="128">
-      <c r="F128" s="4" t="n"/>
-      <c r="I128" s="4" t="n"/>
+      <c r="G128" s="4" t="n"/>
+      <c r="J128" s="4" t="n"/>
     </row>
     <row r="129">
-      <c r="F129" s="4" t="n"/>
-      <c r="I129" s="4" t="n"/>
+      <c r="G129" s="4" t="n"/>
+      <c r="J129" s="4" t="n"/>
     </row>
     <row r="130">
-      <c r="F130" s="4" t="n"/>
-      <c r="I130" s="4" t="n"/>
+      <c r="G130" s="4" t="n"/>
+      <c r="J130" s="4" t="n"/>
     </row>
     <row r="131">
-      <c r="F131" s="4" t="n"/>
-      <c r="I131" s="4" t="n"/>
+      <c r="G131" s="4" t="n"/>
+      <c r="J131" s="4" t="n"/>
     </row>
     <row r="132">
-      <c r="F132" s="4" t="n"/>
-      <c r="I132" s="4" t="n"/>
+      <c r="G132" s="4" t="n"/>
+      <c r="J132" s="4" t="n"/>
     </row>
     <row r="133">
-      <c r="F133" s="4" t="n"/>
-      <c r="I133" s="4" t="n"/>
+      <c r="G133" s="4" t="n"/>
+      <c r="J133" s="4" t="n"/>
     </row>
     <row r="134">
-      <c r="F134" s="4" t="n"/>
-      <c r="I134" s="4" t="n"/>
+      <c r="G134" s="4" t="n"/>
+      <c r="J134" s="4" t="n"/>
     </row>
     <row r="135">
-      <c r="F135" s="4" t="n"/>
-      <c r="I135" s="4" t="n"/>
+      <c r="G135" s="4" t="n"/>
+      <c r="J135" s="4" t="n"/>
     </row>
     <row r="136">
-      <c r="F136" s="4" t="n"/>
-      <c r="I136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
     </row>
     <row r="137">
-      <c r="F137" s="4" t="n"/>
-      <c r="I137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+      <c r="J137" s="4" t="n"/>
     </row>
     <row r="138">
-      <c r="F138" s="4" t="n"/>
-      <c r="I138" s="4" t="n"/>
+      <c r="G138" s="4" t="n"/>
+      <c r="J138" s="4" t="n"/>
     </row>
     <row r="139">
-      <c r="F139" s="4" t="n"/>
-      <c r="I139" s="4" t="n"/>
+      <c r="G139" s="4" t="n"/>
+      <c r="J139" s="4" t="n"/>
     </row>
     <row r="140">
-      <c r="F140" s="4" t="n"/>
-      <c r="I140" s="4" t="n"/>
+      <c r="G140" s="4" t="n"/>
+      <c r="J140" s="4" t="n"/>
     </row>
     <row r="141">
-      <c r="F141" s="4" t="n"/>
-      <c r="I141" s="4" t="n"/>
+      <c r="G141" s="4" t="n"/>
+      <c r="J141" s="4" t="n"/>
     </row>
     <row r="142">
-      <c r="F142" s="4" t="n"/>
-      <c r="I142" s="4" t="n"/>
+      <c r="G142" s="4" t="n"/>
+      <c r="J142" s="4" t="n"/>
     </row>
     <row r="143">
-      <c r="F143" s="4" t="n"/>
-      <c r="I143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
     </row>
     <row r="144">
-      <c r="F144" s="4" t="n"/>
-      <c r="I144" s="4" t="n"/>
+      <c r="G144" s="4" t="n"/>
+      <c r="J144" s="4" t="n"/>
     </row>
     <row r="145">
-      <c r="F145" s="4" t="n"/>
-      <c r="I145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
+      <c r="J145" s="4" t="n"/>
     </row>
     <row r="146">
-      <c r="F146" s="4" t="n"/>
-      <c r="I146" s="4" t="n"/>
+      <c r="G146" s="4" t="n"/>
+      <c r="J146" s="4" t="n"/>
     </row>
     <row r="147">
-      <c r="F147" s="4" t="n"/>
-      <c r="I147" s="4" t="n"/>
+      <c r="G147" s="4" t="n"/>
+      <c r="J147" s="4" t="n"/>
     </row>
     <row r="148">
-      <c r="F148" s="4" t="n"/>
-      <c r="I148" s="4" t="n"/>
+      <c r="G148" s="4" t="n"/>
+      <c r="J148" s="4" t="n"/>
     </row>
     <row r="149">
-      <c r="F149" s="4" t="n"/>
-      <c r="I149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+      <c r="J149" s="4" t="n"/>
     </row>
     <row r="150">
-      <c r="F150" s="4" t="n"/>
-      <c r="I150" s="4" t="n"/>
+      <c r="G150" s="4" t="n"/>
+      <c r="J150" s="4" t="n"/>
     </row>
     <row r="151">
-      <c r="F151" s="4" t="n"/>
-      <c r="I151" s="4" t="n"/>
+      <c r="G151" s="4" t="n"/>
+      <c r="J151" s="4" t="n"/>
     </row>
     <row r="152">
-      <c r="F152" s="4" t="n"/>
-      <c r="I152" s="4" t="n"/>
+      <c r="G152" s="4" t="n"/>
+      <c r="J152" s="4" t="n"/>
     </row>
     <row r="153">
-      <c r="F153" s="4" t="n"/>
-      <c r="I153" s="4" t="n"/>
+      <c r="G153" s="4" t="n"/>
+      <c r="J153" s="4" t="n"/>
     </row>
     <row r="154">
-      <c r="F154" s="4" t="n"/>
-      <c r="I154" s="4" t="n"/>
+      <c r="G154" s="4" t="n"/>
+      <c r="J154" s="4" t="n"/>
     </row>
     <row r="155">
-      <c r="F155" s="4" t="n"/>
-      <c r="I155" s="4" t="n"/>
+      <c r="G155" s="4" t="n"/>
+      <c r="J155" s="4" t="n"/>
     </row>
     <row r="156">
-      <c r="F156" s="4" t="n"/>
-      <c r="I156" s="4" t="n"/>
+      <c r="G156" s="4" t="n"/>
+      <c r="J156" s="4" t="n"/>
     </row>
     <row r="157">
-      <c r="F157" s="4" t="n"/>
-      <c r="I157" s="4" t="n"/>
+      <c r="G157" s="4" t="n"/>
+      <c r="J157" s="4" t="n"/>
     </row>
     <row r="158">
-      <c r="F158" s="4" t="n"/>
-      <c r="I158" s="4" t="n"/>
+      <c r="G158" s="4" t="n"/>
+      <c r="J158" s="4" t="n"/>
     </row>
     <row r="159">
-      <c r="F159" s="4" t="n"/>
-      <c r="I159" s="4" t="n"/>
+      <c r="G159" s="4" t="n"/>
+      <c r="J159" s="4" t="n"/>
     </row>
     <row r="160">
-      <c r="F160" s="4" t="n"/>
-      <c r="I160" s="4" t="n"/>
+      <c r="G160" s="4" t="n"/>
+      <c r="J160" s="4" t="n"/>
     </row>
     <row r="161">
-      <c r="F161" s="4" t="n"/>
-      <c r="I161" s="4" t="n"/>
+      <c r="G161" s="4" t="n"/>
+      <c r="J161" s="4" t="n"/>
     </row>
     <row r="162">
-      <c r="F162" s="4" t="n"/>
-      <c r="I162" s="4" t="n"/>
+      <c r="G162" s="4" t="n"/>
+      <c r="J162" s="4" t="n"/>
     </row>
     <row r="163">
-      <c r="F163" s="4" t="n"/>
-      <c r="I163" s="4" t="n"/>
+      <c r="G163" s="4" t="n"/>
+      <c r="J163" s="4" t="n"/>
     </row>
     <row r="164">
-      <c r="F164" s="4" t="n"/>
-      <c r="I164" s="4" t="n"/>
+      <c r="G164" s="4" t="n"/>
+      <c r="J164" s="4" t="n"/>
     </row>
     <row r="165">
-      <c r="F165" s="4" t="n"/>
-      <c r="I165" s="4" t="n"/>
+      <c r="G165" s="4" t="n"/>
+      <c r="J165" s="4" t="n"/>
     </row>
     <row r="166">
-      <c r="F166" s="4" t="n"/>
-      <c r="I166" s="4" t="n"/>
+      <c r="G166" s="4" t="n"/>
+      <c r="J166" s="4" t="n"/>
     </row>
     <row r="167">
-      <c r="F167" s="4" t="n"/>
-      <c r="I167" s="4" t="n"/>
+      <c r="G167" s="4" t="n"/>
+      <c r="J167" s="4" t="n"/>
     </row>
     <row r="168">
-      <c r="F168" s="4" t="n"/>
-      <c r="I168" s="4" t="n"/>
+      <c r="G168" s="4" t="n"/>
+      <c r="J168" s="4" t="n"/>
     </row>
     <row r="169">
-      <c r="F169" s="4" t="n"/>
-      <c r="I169" s="4" t="n"/>
+      <c r="G169" s="4" t="n"/>
+      <c r="J169" s="4" t="n"/>
     </row>
     <row r="170">
-      <c r="F170" s="4" t="n"/>
-      <c r="I170" s="4" t="n"/>
+      <c r="G170" s="4" t="n"/>
+      <c r="J170" s="4" t="n"/>
     </row>
     <row r="171">
-      <c r="F171" s="4" t="n"/>
-      <c r="I171" s="4" t="n"/>
+      <c r="G171" s="4" t="n"/>
+      <c r="J171" s="4" t="n"/>
     </row>
     <row r="172">
-      <c r="F172" s="4" t="n"/>
-      <c r="I172" s="4" t="n"/>
+      <c r="G172" s="4" t="n"/>
+      <c r="J172" s="4" t="n"/>
     </row>
     <row r="173">
-      <c r="F173" s="4" t="n"/>
-      <c r="I173" s="4" t="n"/>
+      <c r="G173" s="4" t="n"/>
+      <c r="J173" s="4" t="n"/>
     </row>
     <row r="174">
-      <c r="F174" s="4" t="n"/>
-      <c r="I174" s="4" t="n"/>
+      <c r="G174" s="4" t="n"/>
+      <c r="J174" s="4" t="n"/>
     </row>
     <row r="175">
-      <c r="F175" s="4" t="n"/>
-      <c r="I175" s="4" t="n"/>
+      <c r="G175" s="4" t="n"/>
+      <c r="J175" s="4" t="n"/>
     </row>
     <row r="176">
-      <c r="F176" s="4" t="n"/>
-      <c r="I176" s="4" t="n"/>
+      <c r="G176" s="4" t="n"/>
+      <c r="J176" s="4" t="n"/>
     </row>
     <row r="177">
-      <c r="F177" s="4" t="n"/>
-      <c r="I177" s="4" t="n"/>
+      <c r="G177" s="4" t="n"/>
+      <c r="J177" s="4" t="n"/>
     </row>
     <row r="178">
-      <c r="F178" s="4" t="n"/>
-      <c r="I178" s="4" t="n"/>
+      <c r="G178" s="4" t="n"/>
+      <c r="J178" s="4" t="n"/>
     </row>
     <row r="179">
-      <c r="F179" s="4" t="n"/>
-      <c r="I179" s="4" t="n"/>
+      <c r="G179" s="4" t="n"/>
+      <c r="J179" s="4" t="n"/>
     </row>
     <row r="180">
-      <c r="F180" s="4" t="n"/>
-      <c r="I180" s="4" t="n"/>
+      <c r="G180" s="4" t="n"/>
+      <c r="J180" s="4" t="n"/>
     </row>
     <row r="181">
-      <c r="F181" s="4" t="n"/>
-      <c r="I181" s="4" t="n"/>
+      <c r="G181" s="4" t="n"/>
+      <c r="J181" s="4" t="n"/>
     </row>
     <row r="182">
-      <c r="F182" s="4" t="n"/>
-      <c r="I182" s="4" t="n"/>
+      <c r="G182" s="4" t="n"/>
+      <c r="J182" s="4" t="n"/>
     </row>
     <row r="183">
-      <c r="F183" s="4" t="n"/>
-      <c r="I183" s="4" t="n"/>
+      <c r="G183" s="4" t="n"/>
+      <c r="J183" s="4" t="n"/>
     </row>
     <row r="184">
-      <c r="F184" s="4" t="n"/>
-      <c r="I184" s="4" t="n"/>
+      <c r="G184" s="4" t="n"/>
+      <c r="J184" s="4" t="n"/>
     </row>
     <row r="185">
-      <c r="F185" s="4" t="n"/>
-      <c r="I185" s="4" t="n"/>
+      <c r="G185" s="4" t="n"/>
+      <c r="J185" s="4" t="n"/>
     </row>
     <row r="186">
-      <c r="F186" s="4" t="n"/>
-      <c r="I186" s="4" t="n"/>
+      <c r="G186" s="4" t="n"/>
+      <c r="J186" s="4" t="n"/>
     </row>
     <row r="187">
-      <c r="F187" s="4" t="n"/>
-      <c r="I187" s="4" t="n"/>
+      <c r="G187" s="4" t="n"/>
+      <c r="J187" s="4" t="n"/>
     </row>
     <row r="188">
-      <c r="F188" s="4" t="n"/>
-      <c r="I188" s="4" t="n"/>
+      <c r="G188" s="4" t="n"/>
+      <c r="J188" s="4" t="n"/>
     </row>
     <row r="189">
-      <c r="F189" s="4" t="n"/>
-      <c r="I189" s="4" t="n"/>
+      <c r="G189" s="4" t="n"/>
+      <c r="J189" s="4" t="n"/>
     </row>
     <row r="190">
-      <c r="F190" s="4" t="n"/>
-      <c r="I190" s="4" t="n"/>
+      <c r="G190" s="4" t="n"/>
+      <c r="J190" s="4" t="n"/>
     </row>
     <row r="191">
-      <c r="F191" s="4" t="n"/>
-      <c r="I191" s="4" t="n"/>
+      <c r="G191" s="4" t="n"/>
+      <c r="J191" s="4" t="n"/>
     </row>
     <row r="192">
-      <c r="F192" s="4" t="n"/>
-      <c r="I192" s="4" t="n"/>
+      <c r="G192" s="4" t="n"/>
+      <c r="J192" s="4" t="n"/>
     </row>
     <row r="193">
-      <c r="F193" s="4" t="n"/>
-      <c r="I193" s="4" t="n"/>
+      <c r="G193" s="4" t="n"/>
+      <c r="J193" s="4" t="n"/>
     </row>
     <row r="194">
-      <c r="F194" s="4" t="n"/>
-      <c r="I194" s="4" t="n"/>
+      <c r="G194" s="4" t="n"/>
+      <c r="J194" s="4" t="n"/>
     </row>
     <row r="195">
-      <c r="F195" s="4" t="n"/>
-      <c r="I195" s="4" t="n"/>
+      <c r="G195" s="4" t="n"/>
+      <c r="J195" s="4" t="n"/>
     </row>
     <row r="196">
-      <c r="F196" s="4" t="n"/>
-      <c r="I196" s="4" t="n"/>
+      <c r="G196" s="4" t="n"/>
+      <c r="J196" s="4" t="n"/>
     </row>
     <row r="197">
-      <c r="F197" s="4" t="n"/>
-      <c r="I197" s="4" t="n"/>
+      <c r="G197" s="4" t="n"/>
+      <c r="J197" s="4" t="n"/>
     </row>
     <row r="198">
-      <c r="F198" s="4" t="n"/>
-      <c r="I198" s="4" t="n"/>
+      <c r="G198" s="4" t="n"/>
+      <c r="J198" s="4" t="n"/>
     </row>
     <row r="199">
-      <c r="F199" s="4" t="n"/>
-      <c r="I199" s="4" t="n"/>
+      <c r="G199" s="4" t="n"/>
+      <c r="J199" s="4" t="n"/>
     </row>
     <row r="200">
-      <c r="F200" s="4" t="n"/>
-      <c r="I200" s="4" t="n"/>
+      <c r="G200" s="4" t="n"/>
+      <c r="J200" s="4" t="n"/>
     </row>
     <row r="201">
-      <c r="F201" s="4" t="n"/>
-      <c r="I201" s="4" t="n"/>
+      <c r="G201" s="4" t="n"/>
+      <c r="J201" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B2:B201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="无效的封面比例" error="请选择原始、3:4 或 1:1" type="list">
       <formula1>"原始,3:4,1:1"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="无效的创作者声明" error="请从下拉列表中选择预定义的创作者声明" type="list">
+    <dataValidation sqref="K2:K201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="无效的创作者声明" error="请从下拉列表中选择预定义的创作者声明" type="list">
       <formula1>"内容无需标注,内容含营销信息,含AI生成内容,含虚构演绎内容,内容为转载,个人观点，仅供参考"</formula1>
     </dataValidation>
   </dataValidations>
